--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -859,7 +859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1058,7 +1058,7 @@
         <v>cache_version</v>
       </c>
       <c r="B25" t="str">
-        <v>1.0.0</v>
+        <v>1.2.0</v>
       </c>
     </row>
     <row r="26">
@@ -1125,16 +1125,70 @@
         <v>Hi Shubham, I have a question about getting started. Name: {name}, Package: {package}.</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>notify_on_visit</v>
+      </c>
+      <c r="B34" t="str">
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>chatbot_enabled</v>
+      </c>
+      <c r="B35" t="str">
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>email_consultation</v>
+      </c>
+      <c r="B36" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shubham,
+I saw your website and I'd like a free review of my business website.
+Thanks!</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>email_package</v>
+      </c>
+      <c r="B37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shubham,
+I'm interested in the {packageName} package (${price}). Can we discuss?
+Thanks!</v>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>email_general</v>
+      </c>
+      <c r="B38" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hi Shubham,
+I visited your website and would like to know more about website modernization.
+Thanks!</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>hero_image</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/media/team/shubham.jpg</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1155,39 +1209,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>hero</v>
+        <v>team</v>
       </c>
       <c r="C2" t="str">
-        <v>hero-1.jpg</v>
+        <v>shubham.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>Shubham Sunny — website modernization expert</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>team</v>
-      </c>
-      <c r="C3" t="str">
-        <v>shubham.jpg</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Professional website developer</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1217,6 +1257,9 @@
       <c r="I1" t="str">
         <v>highlights</v>
       </c>
+      <c r="J1" t="str">
+        <v>bento</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1232,7 +1275,7 @@
         <v>massive-data-explorer</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>cover.jpg</v>
       </c>
       <c r="F2" t="str">
         <v>Data &amp; Analytics</v>
@@ -1245,6 +1288,9 @@
       </c>
       <c r="I2" t="str">
         <v>Full-stack data explorer over 1M records|Server-side search, filter, and sort|Production deploy with comprehensive test coverage</v>
+      </c>
+      <c r="J2" t="str">
+        <v>feature</v>
       </c>
     </row>
     <row r="3">
@@ -1261,7 +1307,7 @@
         <v>offline-first</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>cover.jpg</v>
       </c>
       <c r="F3" t="str">
         <v>Retail</v>
@@ -1274,6 +1320,9 @@
       </c>
       <c r="I3" t="str">
         <v>Shop and checkout without connectivity|Automatic sync when back online|Production PWA deployed on Render</v>
+      </c>
+      <c r="J3" t="str">
+        <v>tall</v>
       </c>
     </row>
     <row r="4">
@@ -1290,7 +1339,7 @@
         <v>sdui</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>cover.jpg</v>
       </c>
       <c r="F4" t="str">
         <v>Enterprise</v>
@@ -1303,6 +1352,9 @@
       </c>
       <c r="I4" t="str">
         <v>JSON-driven pages and forms|Role-based access from one schema|Live studio for schema inspection</v>
+      </c>
+      <c r="J4" t="str">
+        <v>wide</v>
       </c>
     </row>
     <row r="5">
@@ -1319,7 +1371,7 @@
         <v>fpp</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>cover.jpg</v>
       </c>
       <c r="F5" t="str">
         <v>SaaS</v>
@@ -1333,10 +1385,205 @@
       <c r="I5" t="str">
         <v>VS Code-style plugin marketplace|Fault isolation per plugin|Production host with E2E tests</v>
       </c>
+      <c r="J5" t="str">
+        <v>standard</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>boutique-hotel</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Boutique Hotel Booking</v>
+      </c>
+      <c r="C6" t="str">
+        <v>hospitality</v>
+      </c>
+      <c r="D6" t="str">
+        <v>boutique-hotel</v>
+      </c>
+      <c r="E6" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Hospitality</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Online bookings up 52% with a mobile-first reservation flow</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Room gallery|Instant booking|Multi-language support</v>
+      </c>
+      <c r="J6" t="str">
+        <v>standard</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>fitness-studio</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fitness Studio Website</v>
+      </c>
+      <c r="C7" t="str">
+        <v>local-business</v>
+      </c>
+      <c r="D7" t="str">
+        <v>fitness-studio</v>
+      </c>
+      <c r="E7" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Health &amp; Fitness</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Class sign-ups doubled after launch</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Class schedules|Trainer profiles|Membership plans</v>
+      </c>
+      <c r="J7" t="str">
+        <v>tall</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>real-estate</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Real Estate Listing Portal</v>
+      </c>
+      <c r="C8" t="str">
+        <v>professional-services</v>
+      </c>
+      <c r="D8" t="str">
+        <v>real-estate</v>
+      </c>
+      <c r="E8" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Real Estate</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Property inquiries increased 38% in 60 days</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Map search|Virtual tours|Lead capture forms</v>
+      </c>
+      <c r="J8" t="str">
+        <v>wide</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>medical-clinic</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Medical Clinic Portal</v>
+      </c>
+      <c r="C9" t="str">
+        <v>healthcare</v>
+      </c>
+      <c r="D9" t="str">
+        <v>medical-clinic</v>
+      </c>
+      <c r="E9" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Healthcare</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Patient appointment requests up 45%</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Doctor profiles|Online appointments|Service pages</v>
+      </c>
+      <c r="J9" t="str">
+        <v>standard</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>law-firm</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Law Firm Website</v>
+      </c>
+      <c r="C10" t="str">
+        <v>professional-services</v>
+      </c>
+      <c r="D10" t="str">
+        <v>law-firm</v>
+      </c>
+      <c r="E10" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Consultation requests grew 33% post-redesign</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Practice areas|Attorney bios|Secure contact forms</v>
+      </c>
+      <c r="J10" t="str">
+        <v>standard</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>fashion-store</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Fashion E-Commerce Store</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ecommerce</v>
+      </c>
+      <c r="D11" t="str">
+        <v>fashion-store</v>
+      </c>
+      <c r="E11" t="str">
+        <v>cover.jpg</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Retail</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Mobile sales increased 61% with faster checkout</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Product catalog|Wishlist|Stripe checkout</v>
+      </c>
+      <c r="J11" t="str">
+        <v>tall</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1397,10 +1644,10 @@
         <v>transform-1</v>
       </c>
       <c r="G2" t="str">
-        <v>before.svg</v>
+        <v>before.jpg</v>
       </c>
       <c r="H2" t="str">
-        <v>after.svg</v>
+        <v>after.jpg</v>
       </c>
       <c r="I2" t="str">
         <v>image</v>
@@ -1429,10 +1676,10 @@
         <v>transform-2</v>
       </c>
       <c r="G3" t="str">
-        <v>before.svg</v>
+        <v>before.jpg</v>
       </c>
       <c r="H3" t="str">
-        <v>after.svg</v>
+        <v>after.jpg</v>
       </c>
       <c r="I3" t="str">
         <v>image</v>
@@ -1461,10 +1708,10 @@
         <v>transform-3</v>
       </c>
       <c r="G4" t="str">
-        <v>before.svg</v>
+        <v>before.jpg</v>
       </c>
       <c r="H4" t="str">
-        <v>after.svg</v>
+        <v>after.jpg</v>
       </c>
       <c r="I4" t="str">
         <v>image</v>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -547,7 +547,7 @@
         <v>Mobile-friendly fixes|Speed improvements|Contact form|1 revision round|Launch support</v>
       </c>
       <c r="G2" t="str">
-        <v>Quick professional upgrade — no full rebuild needed.</v>
+        <v>Targeted fixes without a full rebuild — good when the structure is fine but mobile and speed need work.</v>
       </c>
       <c r="H2" t="str">
         <v>yes</v>
@@ -582,7 +582,7 @@
         <v>Full visual redesign|Up to 5 pages|Mobile-first|Basic SEO|WhatsApp link|2 revision rounds</v>
       </c>
       <c r="G3" t="str">
-        <v>Complete trust makeover — our most popular for small businesses.</v>
+        <v>Full redesign — our most common pick for small businesses ready to look current online.</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -617,7 +617,7 @@
         <v>Everything in Business|Blog setup|Analytics|Lead forms|Priority support|3 revision rounds</v>
       </c>
       <c r="G4" t="str">
-        <v>For businesses ready to capture more leads online.</v>
+        <v>Everything in Business plus blog, analytics, and lead forms for growing companies.</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -1885,7 +1885,7 @@
         <v>Thin attorney bios, broken mobile layout, unencrypted contact form.</v>
       </c>
       <c r="K10" t="str">
-        <v>Premium redesign with credentials, practice area detail, and encrypted intake.</v>
+        <v>Professional redesign with credentials, practice area detail, and encrypted intake.</v>
       </c>
       <c r="L10" t="str">
         <v>Consultation requests up 55% in Q1.</v>
@@ -1985,7 +1985,7 @@
         <v>what-mobile-friendly-means</v>
       </c>
       <c r="B3" t="str">
-        <v>What Mobile-Friendly Actually Means (Plain English)</v>
+        <v>What Mobile-Friendly Actually Means</v>
       </c>
       <c r="C3" t="str">
         <v>No jargon — just what mobile-friendly means for your business and why it matters for US customers.</v>
@@ -2036,10 +2036,10 @@
         <v>why-we-do-not-take-every-project</v>
       </c>
       <c r="B6" t="str">
-        <v>Why We Do Not Take Every Project</v>
+        <v>What It's Like Working With Us</v>
       </c>
       <c r="C6" t="str">
-        <v>We say no to most inquiries on purpose. Here is what we look for — and what you get when we say yes.</v>
+        <v>Eight years and 163+ projects in — here's how we actually work, from first message to handoff.</v>
       </c>
       <c r="D6" t="str">
         <v>published</v>
@@ -2122,7 +2122,7 @@
         <v>Founder &amp; Lead Developer</v>
       </c>
       <c r="C2" t="str">
-        <v>8+ years · Founder</v>
+        <v>8+ years · Founder since 2018</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -2131,7 +2131,7 @@
         <v>Full-Stack|Web Apps|Data Scraping|Custom Software</v>
       </c>
       <c r="F2" t="str">
-        <v>I founded this studio and own technical direction on every project — architecture, code quality, and client outcomes. We scale with trusted specialists per project, not a bloated bench for show.</v>
+        <v>I started freelancing on Fiverr in 2018 and built this into a small studio over eight years. I still review architecture and code on every project — websites, scrapers, and custom apps for clients who need someone reliable.</v>
       </c>
       <c r="G2" t="str">
         <v>A website should make a stranger feel confident enough to call you.</v>
@@ -2169,7 +2169,7 @@
         <v>Manual QA|Automation Testing|Client Onboarding|UAT</v>
       </c>
       <c r="F3" t="str">
-        <v>Deep handles the rest of day-to-day delivery — QA on real devices, client kickoff calls, milestone tracking, and making sure nothing goes live until it is right.</v>
+        <v>Deep has been with us for years handling QA on real devices, client kickoff calls, milestone tracking, and making sure nothing goes live until it passes her checklist.</v>
       </c>
       <c r="G3" t="str">
         <v>Quality is not a phase — it is the reason clients come back.</v>
@@ -2207,7 +2207,7 @@
         <v>HR Operations|Talent Hiring|Brand Marketing|Client Outreach</v>
       </c>
       <c r="F4" t="str">
-        <v>Shushma builds and runs the people side — hiring, culture, marketing outreach, and keeping the right specialists on every project.</v>
+        <v>Shushma runs hiring, team culture, and client outreach — the reason we can keep the same trusted people on projects instead of rotating strangers.</v>
       </c>
       <c r="G4" t="str">
         <v>Great delivery starts with great people — and great people need clear direction.</v>
@@ -2245,7 +2245,7 @@
         <v>Program Management|Agile Delivery|Enterprise Clients|Mentoring</v>
       </c>
       <c r="F5" t="str">
-        <v>Vinay handles program management on larger builds — timelines, milestones, and mentoring developers through complex delivery.</v>
+        <v>Vinay manages timelines and delivery on larger builds — weekly check-ins, milestone tracking, and keeping complex projects moving without surprises.</v>
       </c>
       <c r="G5" t="str">
         <v>Ship on time, communicate early, and never hide bad news.</v>
@@ -2384,7 +2384,7 @@
         <v>Professional Services</v>
       </c>
       <c r="D4" t="str">
-        <v>Generic template → premium look that matches their reputation. Clear practice areas and a simple contact form.</v>
+        <v>Generic template → professional look that matches their reputation. Clear practice areas and a simple contact form.</v>
       </c>
       <c r="E4" t="str">
         <v>Growth Website</v>
@@ -2718,7 +2718,7 @@
         <v>shubham.jpg</v>
       </c>
       <c r="D2" t="str">
-        <v>Shubham Sunny — founder &amp; lead developer</v>
+        <v>Shubham Sunny — website modernization expert</v>
       </c>
     </row>
   </sheetData>
@@ -2742,15 +2742,15 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Do you take every project?</v>
+        <v>How long has your team been in business?</v>
       </c>
       <c r="B2" t="str">
-        <v>Not every one. We pick work where the goal is clear and we can do it properly — if we say yes, you get our full attention.</v>
+        <v>Since 2018 — about 8 years now. Most clients find us on Fiverr or through referrals. We have delivered 163+ projects across websites, data scraping, and custom software.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Website modernization — what do I get?</v>
+        <v>What is included in a website modernization project?</v>
       </c>
       <c r="B3" t="str">
         <v>A mobile-first site that loads fast and makes calling or booking easy. Hosting, SSL, and handoff included.</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Is data scraping legal?</v>
+        <v>Is web data scraping legal and compliant?</v>
       </c>
       <c r="B4" t="str">
         <v>We collect publicly visible data only — no private logins. Every project starts with a scope review.</v>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>What is custom software?</v>
+        <v>What does custom software development include?</v>
       </c>
       <c r="B5" t="str">
         <v>Web apps, mobile apps, bots, and tools built for your workflow when off-the-shelf products do not fit.</v>
@@ -2777,7 +2777,7 @@
         <v>Price and timeline?</v>
       </c>
       <c r="B6" t="str">
-        <v>Websites from ~$800. Scraping from ~$200. Custom software after discovery. Most web projects: 2–4 weeks.</v>
+        <v>Websites from $499 (Starter Refresh). Business modernization from $1,499. Scraping from ~$200. Custom software after discovery. Most web projects: 2–4 weeks.</v>
       </c>
     </row>
     <row r="7">
@@ -2845,7 +2845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2868,7 +2868,7 @@
         <v>tagline</v>
       </c>
       <c r="B3" t="str">
-        <v>Premium Development · Vision-First Clients Only</v>
+        <v>Website &amp; Software Development · Since 2018</v>
       </c>
     </row>
     <row r="4">
@@ -2956,7 +2956,7 @@
         <v>certifications</v>
       </c>
       <c r="B14" t="str">
-        <v>8+ Years Experience</v>
+        <v>8+ Years · Since 2018</v>
       </c>
     </row>
     <row r="15">
@@ -2964,7 +2964,7 @@
         <v>headline</v>
       </c>
       <c r="B15" t="str">
-        <v>Developers for Businesses With a Vision</v>
+        <v>I help businesses fix websites, scrape data, and build software that works</v>
       </c>
     </row>
     <row r="16">
@@ -2972,7 +2972,7 @@
         <v>bio_short</v>
       </c>
       <c r="B16" t="str">
-        <v>We are a selective development studio — we partner with premium clients who know where they are going, not businesses looking for the cheapest quote.</v>
+        <v>I've been building websites and custom software for US and global clients since 2018 — 163+ projects, mostly repeat work and referrals.</v>
       </c>
     </row>
     <row r="17">
@@ -2980,7 +2980,7 @@
         <v>bio_long</v>
       </c>
       <c r="B17" t="str">
-        <v>We do not take every project. If you have a clear goal and care about quality, we can talk. Websites, data work, and custom software — founder-led, with a small core team and trusted specialists when a build needs extra hands.</v>
+        <v>Eight years in, the work is still straightforward: understand what you need, build it properly, and hand it over with clear docs so you are not stuck for every small change. I review every project personally. Deep handles QA, Shushma runs people and outreach, and Vinay keeps larger builds on track.</v>
       </c>
     </row>
     <row r="18">
@@ -3020,7 +3020,7 @@
         <v>hero_overline</v>
       </c>
       <c r="B22" t="str">
-        <v>Premium Development Studio</v>
+        <v>8+ Years · Websites &amp; Software</v>
       </c>
     </row>
     <row r="23">
@@ -3044,7 +3044,7 @@
         <v>intro</v>
       </c>
       <c r="B25" t="str">
-        <v>A selective team of developers for premium clients with a vision — not a factory that takes every job. If you care about quality, clarity, and long-term results, you are in the right place.</v>
+        <v>Founder-led studio since 2018 — websites, data scraping, and custom software for business owners who want someone accountable, not a faceless agency.</v>
       </c>
     </row>
     <row r="26">
@@ -3068,7 +3068,7 @@
         <v>artist_philosophy</v>
       </c>
       <c r="B28" t="str">
-        <v>We say no to most inquiries — so the yes means something.</v>
+        <v>I'd rather take a week longer and ship something solid than rush something you'll need fixed in a month.</v>
       </c>
     </row>
     <row r="29">
@@ -3100,7 +3100,7 @@
         <v>seo_description</v>
       </c>
       <c r="B32" t="str">
-        <v>Founder-led studio helping businesses modernize websites, scrape data at scale, and build custom software. 8+ years, 163+ projects. Based in India, serving US &amp; global clients.</v>
+        <v>Founder-led development since 2018 — website modernization, data scraping, and custom software. 8+ years, 163+ projects. Based in India, serving US &amp; global clients.</v>
       </c>
     </row>
     <row r="33">
@@ -3156,7 +3156,7 @@
         <v>hero_status</v>
       </c>
       <c r="B39" t="str">
-        <v>Select projects · High standards</v>
+        <v>8+ years in business · Reply within 24h</v>
       </c>
     </row>
     <row r="40">
@@ -3164,7 +3164,7 @@
         <v>selectivity_line</v>
       </c>
       <c r="B40" t="str">
-        <v>We do not work with everyone — only with clients who have a vision, clear goals, and the standards to match.</v>
+        <v>8 years · 120+ clients · Founder-led on every project</v>
       </c>
     </row>
     <row r="41">
@@ -3172,12 +3172,28 @@
         <v>standards</v>
       </c>
       <c r="B41" t="str">
-        <v>Vision-first clients|Hands-on founder review|Selective engagements|No cookie-cutter work</v>
+        <v>8+ years experience|Founder reviews every build|US &amp; UK time zones|Clear pricing upfront</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>contact_quote</v>
+      </c>
+      <c r="B42" t="str">
+        <v>I've been running this studio since 2018. If we take your project, you talk to real people — not a ticket queue — and get straight answers on timeline and cost.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>team_intro</v>
+      </c>
+      <c r="B43" t="str">
+        <v>A small core team we have worked with for years — founder-led development, QA, delivery, and HR. For bigger builds we bring in trusted specialists, not random freelancers.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B43"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3229,7 +3245,7 @@
         <v>Mobile-friendly fixes|Speed improvements|Contact form setup|1 revision round|Launch support</v>
       </c>
       <c r="F2" t="str">
-        <v>For sites that need a quick professional upgrade without a full rebuild.</v>
+        <v>Quick fixes when your site mostly works but looks dated or slow on phones.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -3255,7 +3271,7 @@
         <v>Full visual redesign|Up to 5 pages|Mobile-first layout|Basic SEO setup|WhatsApp / chat link|2 revision rounds</v>
       </c>
       <c r="F3" t="str">
-        <v>Our most popular package — a complete trust makeover for your business.</v>
+        <v>Full redesign for small businesses — the package most clients pick when their site needs a proper refresh, not just a patch.</v>
       </c>
       <c r="G3" t="str">
         <v>yes</v>
@@ -3281,7 +3297,7 @@
         <v>Everything in Business Modern|Blog setup|Analytics &amp; insights|Lead capture forms|Priority support|3 revision rounds</v>
       </c>
       <c r="F4" t="str">
-        <v>For businesses ready to grow online and capture more leads.</v>
+        <v>For businesses that want blog, analytics, and lead capture built in from day one.</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -3825,7 +3841,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3844,9 +3860,6 @@
         <v>keywords</v>
       </c>
       <c r="F1" t="str">
-        <v>gallery_category</v>
-      </c>
-      <c r="G1" t="str">
         <v>featured_package_id</v>
       </c>
     </row>
@@ -3867,9 +3880,6 @@
         <v>small business website redesign, website makeover small business</v>
       </c>
       <c r="F2" t="str">
-        <v>local-business</v>
-      </c>
-      <c r="G2" t="str">
         <v>business-modern</v>
       </c>
     </row>
@@ -3890,9 +3900,6 @@
         <v>modernize outdated website, old website redesign</v>
       </c>
       <c r="F3" t="str">
-        <v>all</v>
-      </c>
-      <c r="G3" t="str">
         <v>business-modern</v>
       </c>
     </row>
@@ -3913,9 +3920,6 @@
         <v>dental website design, dentist website redesign</v>
       </c>
       <c r="F4" t="str">
-        <v>healthcare</v>
-      </c>
-      <c r="G4" t="str">
         <v>growth-site</v>
       </c>
     </row>
@@ -3936,9 +3940,6 @@
         <v>restaurant website redesign, food business website</v>
       </c>
       <c r="F5" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="G5" t="str">
         <v>starter-refresh</v>
       </c>
     </row>
@@ -3953,21 +3954,18 @@
         <v>Websites for Professional Services</v>
       </c>
       <c r="D6" t="str">
-        <v>Premium websites for lawyers, consultants, and service businesses. Look credible, get more inquiries.</v>
+        <v>Professional websites for lawyers, consultants, and service businesses. Look credible, get more inquiries.</v>
       </c>
       <c r="E6" t="str">
         <v>professional services website, law firm website design</v>
       </c>
       <c r="F6" t="str">
-        <v>professional-services</v>
-      </c>
-      <c r="G6" t="str">
         <v>growth-site</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4109,7 +4107,7 @@
         <v>#3B82F6</v>
       </c>
       <c r="D2" t="str">
-        <v>Turn outdated sites into trust-building machines</v>
+        <v>Modern sites that load fast and get you more calls</v>
       </c>
       <c r="E2" t="str">
         <v>Modern, mobile-first websites that convert visitors into customers.</v>

--- a/site-data.xlsx
+++ b/site-data.xlsx
@@ -851,7 +851,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -864,12 +864,9 @@
         <v>category</v>
       </c>
       <c r="D1" t="str">
-        <v>thumbnail</v>
+        <v>download_url</v>
       </c>
       <c r="E1" t="str">
-        <v>download_url</v>
-      </c>
-      <c r="F1" t="str">
         <v>description</v>
       </c>
     </row>
@@ -884,12 +881,9 @@
         <v>Business</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E2" t="str">
-        <v>#</v>
-      </c>
-      <c r="F2" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -904,12 +898,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E3" t="str">
-        <v>#</v>
-      </c>
-      <c r="F3" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -924,12 +915,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E4" t="str">
-        <v>#</v>
-      </c>
-      <c r="F4" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -944,12 +932,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E5" t="str">
-        <v>#</v>
-      </c>
-      <c r="F5" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -964,12 +949,9 @@
         <v>Healthcare</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E6" t="str">
-        <v>#</v>
-      </c>
-      <c r="F6" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -984,12 +966,9 @@
         <v>Business</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E7" t="str">
-        <v>#</v>
-      </c>
-      <c r="F7" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1004,12 +983,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E8" t="str">
-        <v>#</v>
-      </c>
-      <c r="F8" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1024,12 +1000,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E9" t="str">
-        <v>#</v>
-      </c>
-      <c r="F9" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1044,12 +1017,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E10" t="str">
-        <v>#</v>
-      </c>
-      <c r="F10" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1064,12 +1034,9 @@
         <v>Healthcare</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E11" t="str">
-        <v>#</v>
-      </c>
-      <c r="F11" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1084,12 +1051,9 @@
         <v>Business</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E12" t="str">
-        <v>#</v>
-      </c>
-      <c r="F12" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1104,12 +1068,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E13" t="str">
-        <v>#</v>
-      </c>
-      <c r="F13" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1124,12 +1085,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E14" t="str">
-        <v>#</v>
-      </c>
-      <c r="F14" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1144,12 +1102,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E15" t="str">
-        <v>#</v>
-      </c>
-      <c r="F15" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1164,12 +1119,9 @@
         <v>Healthcare</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E16" t="str">
-        <v>#</v>
-      </c>
-      <c r="F16" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1184,12 +1136,9 @@
         <v>Business</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E17" t="str">
-        <v>#</v>
-      </c>
-      <c r="F17" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1204,12 +1153,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E18" t="str">
-        <v>#</v>
-      </c>
-      <c r="F18" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1224,12 +1170,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E19" t="str">
-        <v>#</v>
-      </c>
-      <c r="F19" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1244,12 +1187,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E20" t="str">
-        <v>#</v>
-      </c>
-      <c r="F20" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1264,12 +1204,9 @@
         <v>Healthcare</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E21" t="str">
-        <v>#</v>
-      </c>
-      <c r="F21" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1284,12 +1221,9 @@
         <v>Business</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E22" t="str">
-        <v>#</v>
-      </c>
-      <c r="F22" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1304,12 +1238,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E23" t="str">
-        <v>#</v>
-      </c>
-      <c r="F23" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1324,12 +1255,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E24" t="str">
-        <v>#</v>
-      </c>
-      <c r="F24" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1344,12 +1272,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E25" t="str">
-        <v>#</v>
-      </c>
-      <c r="F25" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1364,12 +1289,9 @@
         <v>Healthcare</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E26" t="str">
-        <v>#</v>
-      </c>
-      <c r="F26" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1384,12 +1306,9 @@
         <v>Business</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E27" t="str">
-        <v>#</v>
-      </c>
-      <c r="F27" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1404,12 +1323,9 @@
         <v>Portfolio</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E28" t="str">
-        <v>#</v>
-      </c>
-      <c r="F28" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1424,12 +1340,9 @@
         <v>E-commerce</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E29" t="str">
-        <v>#</v>
-      </c>
-      <c r="F29" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1444,12 +1357,9 @@
         <v>Restaurant</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E30" t="str">
-        <v>#</v>
-      </c>
-      <c r="F30" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
@@ -1464,18 +1374,15 @@
         <v>Healthcare</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>#</v>
       </c>
       <c r="E31" t="str">
-        <v>#</v>
-      </c>
-      <c r="F31" t="str">
         <v>Free responsive website template — ready to customize and deploy.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2074,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:K5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2087,30 +1994,27 @@
         <v>certification</v>
       </c>
       <c r="D1" t="str">
-        <v>past_company</v>
+        <v>expertise</v>
       </c>
       <c r="E1" t="str">
-        <v>expertise</v>
+        <v>bio</v>
       </c>
       <c r="F1" t="str">
-        <v>bio</v>
+        <v>philosophy</v>
       </c>
       <c r="G1" t="str">
-        <v>philosophy</v>
+        <v>image_path</v>
       </c>
       <c r="H1" t="str">
-        <v>image_path</v>
+        <v>is_founder</v>
       </c>
       <c r="I1" t="str">
-        <v>is_founder</v>
+        <v>linkedin</v>
       </c>
       <c r="J1" t="str">
-        <v>linkedin</v>
+        <v>phone</v>
       </c>
       <c r="K1" t="str">
-        <v>phone</v>
-      </c>
-      <c r="L1" t="str">
         <v>order</v>
       </c>
     </row>
@@ -2125,30 +2029,27 @@
         <v>8+ years · Founder since 2018</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Full-Stack|Web Apps|Data Scraping|Custom Software</v>
       </c>
       <c r="E2" t="str">
-        <v>Full-Stack|Web Apps|Data Scraping|Custom Software</v>
+        <v>I started freelancing on Fiverr in 2018 and built this into a small studio over eight years. I still review architecture and code on every project — websites, scrapers, and custom apps for clients who need someone reliable.</v>
       </c>
       <c r="F2" t="str">
-        <v>I started freelancing on Fiverr in 2018 and built this into a small studio over eight years. I still review architecture and code on every project — websites, scrapers, and custom apps for clients who need someone reliable.</v>
+        <v>A website should make a stranger feel confident enough to call you.</v>
       </c>
       <c r="G2" t="str">
-        <v>A website should make a stranger feel confident enough to call you.</v>
+        <v>shubham.jpg</v>
       </c>
       <c r="H2" t="str">
-        <v>shubham.jpg</v>
+        <v>yes</v>
       </c>
       <c r="I2" t="str">
-        <v>yes</v>
+        <v>https://www.linkedin.com/in/shubham-sunny-09b013129/</v>
       </c>
       <c r="J2" t="str">
-        <v>https://www.linkedin.com/in/shubham-sunny-09b013129/</v>
-      </c>
-      <c r="K2" t="str">
         <v>+91 97718 23804</v>
       </c>
-      <c r="L2">
+      <c r="K2">
         <v>1</v>
       </c>
     </row>
@@ -2163,30 +2064,27 @@
         <v>Quality Assurance Expert</v>
       </c>
       <c r="D3" t="str">
+        <v>Manual QA|Automation Testing|Client Onboarding|UAT</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Deep has been with us for years handling QA on real devices, client kickoff calls, milestone tracking, and making sure nothing goes live until it passes her checklist.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Quality is not a phase — it is the reason clients come back.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>deep-shikha.png</v>
+      </c>
+      <c r="H3" t="str">
         <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>Manual QA|Automation Testing|Client Onboarding|UAT</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Deep has been with us for years handling QA on real devices, client kickoff calls, milestone tracking, and making sure nothing goes live until it passes her checklist.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Quality is not a phase — it is the reason clients come back.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>deep-shikha.png</v>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
         <v>+91 9142760891</v>
       </c>
-      <c r="L3">
+      <c r="K3">
         <v>2</v>
       </c>
     </row>
@@ -2201,30 +2099,27 @@
         <v>People &amp; Growth</v>
       </c>
       <c r="D4" t="str">
+        <v>HR Operations|Talent Hiring|Brand Marketing|Client Outreach</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Shushma runs hiring, team culture, and client outreach — the reason we can keep the same trusted people on projects instead of rotating strangers.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Great delivery starts with great people — and great people need clear direction.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>shushma-devi.png</v>
+      </c>
+      <c r="H4" t="str">
         <v/>
-      </c>
-      <c r="E4" t="str">
-        <v>HR Operations|Talent Hiring|Brand Marketing|Client Outreach</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Shushma runs hiring, team culture, and client outreach — the reason we can keep the same trusted people on projects instead of rotating strangers.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Great delivery starts with great people — and great people need clear direction.</v>
-      </c>
-      <c r="H4" t="str">
-        <v>shushma-devi.png</v>
       </c>
       <c r="I4" t="str">
         <v/>
       </c>
       <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
         <v>+91 9939067781</v>
       </c>
-      <c r="L4">
+      <c r="K4">
         <v>3</v>
       </c>
     </row>
@@ -2239,43 +2134,40 @@
         <v>Program &amp; delivery</v>
       </c>
       <c r="D5" t="str">
+        <v>Program Management|Agile Delivery|Enterprise Clients|Mentoring</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Vinay manages timelines and delivery on larger builds — weekly check-ins, milestone tracking, and keeping complex projects moving without surprises.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Ship on time, communicate early, and never hide bad news.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>vinay-thakur.png</v>
+      </c>
+      <c r="H5" t="str">
         <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>Program Management|Agile Delivery|Enterprise Clients|Mentoring</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Vinay manages timelines and delivery on larger builds — weekly check-ins, milestone tracking, and keeping complex projects moving without surprises.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Ship on time, communicate early, and never hide bad news.</v>
-      </c>
-      <c r="H5" t="str">
-        <v>vinay-thakur.png</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
       <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
         <v>+91 9931230810</v>
       </c>
-      <c r="L5">
+      <c r="K5">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2302,12 +2194,6 @@
       <c r="H1" t="str">
         <v>after_file</v>
       </c>
-      <c r="I1" t="str">
-        <v>before_type</v>
-      </c>
-      <c r="J1" t="str">
-        <v>after_type</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2334,12 +2220,6 @@
       <c r="H2" t="str">
         <v>after.jpg</v>
       </c>
-      <c r="I2" t="str">
-        <v>image</v>
-      </c>
-      <c r="J2" t="str">
-        <v>image</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2366,12 +2246,6 @@
       <c r="H3" t="str">
         <v>after.jpg</v>
       </c>
-      <c r="I3" t="str">
-        <v>image</v>
-      </c>
-      <c r="J3" t="str">
-        <v>image</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2398,16 +2272,10 @@
       <c r="H4" t="str">
         <v>after.jpg</v>
       </c>
-      <c r="I4" t="str">
-        <v>image</v>
-      </c>
-      <c r="J4" t="str">
-        <v>image</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3315,7 +3183,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3340,12 +3208,9 @@
         <v>date</v>
       </c>
       <c r="H1" t="str">
-        <v>image</v>
+        <v>source_url</v>
       </c>
       <c r="I1" t="str">
-        <v>source_url</v>
-      </c>
-      <c r="J1" t="str">
         <v>featured</v>
       </c>
     </row>
@@ -3372,12 +3237,9 @@
         <v>2024</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I2" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J2" t="str">
         <v>yes</v>
       </c>
     </row>
@@ -3404,12 +3266,9 @@
         <v>2024</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I3" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J3" t="str">
         <v>yes</v>
       </c>
     </row>
@@ -3436,12 +3295,9 @@
         <v>2023</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I4" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J4" t="str">
         <v>yes</v>
       </c>
     </row>
@@ -3468,12 +3324,9 @@
         <v>2023</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I5" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J5" t="str">
         <v/>
       </c>
     </row>
@@ -3500,12 +3353,9 @@
         <v>2023</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I6" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J6" t="str">
         <v>yes</v>
       </c>
     </row>
@@ -3532,12 +3382,9 @@
         <v>2023</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I7" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J7" t="str">
         <v/>
       </c>
     </row>
@@ -3564,12 +3411,9 @@
         <v>2023</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I8" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J8" t="str">
         <v/>
       </c>
     </row>
@@ -3596,12 +3440,9 @@
         <v>2023</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I9" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J9" t="str">
         <v/>
       </c>
     </row>
@@ -3628,12 +3469,9 @@
         <v>2023</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I10" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J10" t="str">
         <v/>
       </c>
     </row>
@@ -3660,12 +3498,9 @@
         <v>2023</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I11" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J11" t="str">
         <v/>
       </c>
     </row>
@@ -3692,12 +3527,9 @@
         <v>2023</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I12" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J12" t="str">
         <v/>
       </c>
     </row>
@@ -3724,25 +3556,22 @@
         <v>2023</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
       <c r="I13" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-      <c r="J13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3770,71 +3599,47 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>twitter_url</v>
+        <v>fiverr_url</v>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>facebook_url</v>
+        <v>github_url</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>https://github.com/ShubhamSahaniNitkkr</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>instagram_url</v>
+        <v>google_reviews_url</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>fiverr_url</v>
+        <v>google_rating</v>
       </c>
       <c r="B7" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>github_url</v>
+        <v>google_total_reviews</v>
       </c>
       <c r="B8" t="str">
-        <v>https://github.com/ShubhamSahaniNitkkr</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>google_reviews_url</v>
-      </c>
-      <c r="B9" t="str">
-        <v>https://www.fiverr.com/shubhamsunny?public_mode=true</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>google_rating</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>google_total_reviews</v>
-      </c>
-      <c r="B11" t="str">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
   </ignoredErrors>
 </worksheet>
 </file>
